--- a/Sim/tables_output_2050.xlsx
+++ b/Sim/tables_output_2050.xlsx
@@ -442,7 +442,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -456,7 +456,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -470,7 +470,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -484,7 +484,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
     </row>
   </sheetData>
@@ -519,10 +519,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -533,10 +533,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -547,10 +547,10 @@
         <v>20</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -561,10 +561,10 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5">
-        <v>1.94</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -630,7 +630,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -644,7 +644,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
     </row>
   </sheetData>
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -721,10 +721,10 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>3.06</v>
+        <v>3.22</v>
       </c>
     </row>
   </sheetData>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -782,10 +782,10 @@
         <v>100</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3">
-        <v>1.94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -816,10 +816,10 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>3.06</v>
+        <v>3.22</v>
       </c>
     </row>
   </sheetData>
